--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0095.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0095.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ta tin rằng chỉ cần có đủ tay đua, một kỵ sĩ sao chân chính sẽ xuất hiện và giữ cho ngọn lửa thi đấu này luôn rực cháy.</t>
+          <t>Tao tin rằng chỉ cần có đủ tay đua, một kỵ sĩ sao chân chính sẽ xuất hiện và giữ cho ngọn lửa thi đấu này luôn rực cháy.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Đi thôi! Haha, giờ khi đã tham gia cuộc đua Startorch, cậu cũng cảm nhận được sự kỳ diệu của nó rồi chứ? Nói ta nghe, cậu thích điều gì nhất?</t>
+          <t>Đi thôi! Haha, giờ khi đã tham gia cuộc đua Startorch, cậu cũng cảm nhận được sự kỳ diệu của nó rồi chứ? Nói tao nghe, cậu thích điều gì nhất?</t>
         </is>
       </c>
     </row>
